--- a/Images/1/10000000StatisticalSeries.xlsx
+++ b/Images/1/10000000StatisticalSeries.xlsx
@@ -492,126 +492,126 @@
     </row>
     <row r="2" spans="1:20">
       <c r="A2">
-        <v>499211</v>
+        <v>501460</v>
       </c>
       <c r="B2">
-        <v>500277</v>
+        <v>499947</v>
       </c>
       <c r="C2">
-        <v>500427</v>
+        <v>501097</v>
       </c>
       <c r="D2">
-        <v>499680</v>
+        <v>500292</v>
       </c>
       <c r="E2">
-        <v>501005</v>
+        <v>499188</v>
       </c>
       <c r="F2">
-        <v>500178</v>
+        <v>500078</v>
       </c>
       <c r="G2">
-        <v>500596</v>
+        <v>500436</v>
       </c>
       <c r="H2">
-        <v>500380</v>
+        <v>500223</v>
       </c>
       <c r="I2">
-        <v>500556</v>
+        <v>499843</v>
       </c>
       <c r="J2">
-        <v>498896</v>
+        <v>498868</v>
       </c>
       <c r="K2">
-        <v>499872</v>
+        <v>501120</v>
       </c>
       <c r="L2">
-        <v>499534</v>
+        <v>497465</v>
       </c>
       <c r="M2">
-        <v>500204</v>
+        <v>499961</v>
       </c>
       <c r="N2">
-        <v>500262</v>
+        <v>500476</v>
       </c>
       <c r="O2">
-        <v>500124</v>
+        <v>499880</v>
       </c>
       <c r="P2">
-        <v>499446</v>
+        <v>499788</v>
       </c>
       <c r="Q2">
-        <v>500377</v>
+        <v>499599</v>
       </c>
       <c r="R2">
-        <v>500044</v>
+        <v>500083</v>
       </c>
       <c r="S2">
-        <v>499815</v>
+        <v>499784</v>
       </c>
       <c r="T2">
-        <v>499116</v>
+        <v>500412</v>
       </c>
     </row>
     <row r="3" spans="1:20">
       <c r="A3">
-        <v>0.0499211</v>
+        <v>0.050146</v>
       </c>
       <c r="B3">
-        <v>0.0500277</v>
+        <v>0.0499947</v>
       </c>
       <c r="C3">
-        <v>0.0500427</v>
+        <v>0.05010970000000001</v>
       </c>
       <c r="D3">
-        <v>0.04996800000000001</v>
+        <v>0.0500292</v>
       </c>
       <c r="E3">
-        <v>0.05010049999999999</v>
+        <v>0.04991879999999999</v>
       </c>
       <c r="F3">
-        <v>0.0500178</v>
+        <v>0.05000779999999999</v>
       </c>
       <c r="G3">
-        <v>0.05005959999999998</v>
+        <v>0.05004360000000002</v>
       </c>
       <c r="H3">
-        <v>0.05003800000000003</v>
+        <v>0.05002230000000002</v>
       </c>
       <c r="I3">
-        <v>0.05005559999999998</v>
+        <v>0.04998429999999998</v>
       </c>
       <c r="J3">
-        <v>0.04988960000000003</v>
+        <v>0.04988680000000001</v>
       </c>
       <c r="K3">
-        <v>0.04998720000000001</v>
+        <v>0.05011200000000005</v>
       </c>
       <c r="L3">
-        <v>0.04995339999999993</v>
+        <v>0.04974649999999992</v>
       </c>
       <c r="M3">
-        <v>0.05002040000000008</v>
+        <v>0.04999609999999999</v>
       </c>
       <c r="N3">
-        <v>0.05002619999999991</v>
+        <v>0.05004760000000008</v>
       </c>
       <c r="O3">
-        <v>0.05001240000000007</v>
+        <v>0.04998799999999992</v>
       </c>
       <c r="P3">
-        <v>0.04994460000000001</v>
+        <v>0.04997879999999999</v>
       </c>
       <c r="Q3">
-        <v>0.05003769999999996</v>
+        <v>0.04995990000000006</v>
       </c>
       <c r="R3">
-        <v>0.05000440000000006</v>
+        <v>0.05000830000000001</v>
       </c>
       <c r="S3">
-        <v>0.04998150000000001</v>
+        <v>0.04997839999999998</v>
       </c>
       <c r="T3">
-        <v>0.04991159999999994</v>
+        <v>0.05004120000000001</v>
       </c>
     </row>
   </sheetData>

--- a/Images/1/10000000StatisticalSeries.xlsx
+++ b/Images/1/10000000StatisticalSeries.xlsx
@@ -492,126 +492,126 @@
     </row>
     <row r="2" spans="1:20">
       <c r="A2">
-        <v>501460</v>
+        <v>499389</v>
       </c>
       <c r="B2">
-        <v>499947</v>
+        <v>498941</v>
       </c>
       <c r="C2">
-        <v>501097</v>
+        <v>500200</v>
       </c>
       <c r="D2">
-        <v>500292</v>
+        <v>500731</v>
       </c>
       <c r="E2">
+        <v>500244</v>
+      </c>
+      <c r="F2">
+        <v>500316</v>
+      </c>
+      <c r="G2">
+        <v>500732</v>
+      </c>
+      <c r="H2">
+        <v>499837</v>
+      </c>
+      <c r="I2">
+        <v>499854</v>
+      </c>
+      <c r="J2">
+        <v>499866</v>
+      </c>
+      <c r="K2">
+        <v>500158</v>
+      </c>
+      <c r="L2">
+        <v>499457</v>
+      </c>
+      <c r="M2">
+        <v>500218</v>
+      </c>
+      <c r="N2">
         <v>499188</v>
       </c>
-      <c r="F2">
-        <v>500078</v>
-      </c>
-      <c r="G2">
-        <v>500436</v>
-      </c>
-      <c r="H2">
-        <v>500223</v>
-      </c>
-      <c r="I2">
-        <v>499843</v>
-      </c>
-      <c r="J2">
-        <v>498868</v>
-      </c>
-      <c r="K2">
-        <v>501120</v>
-      </c>
-      <c r="L2">
-        <v>497465</v>
-      </c>
-      <c r="M2">
-        <v>499961</v>
-      </c>
-      <c r="N2">
-        <v>500476</v>
-      </c>
       <c r="O2">
-        <v>499880</v>
+        <v>500880</v>
       </c>
       <c r="P2">
-        <v>499788</v>
+        <v>500245</v>
       </c>
       <c r="Q2">
-        <v>499599</v>
+        <v>499287</v>
       </c>
       <c r="R2">
-        <v>500083</v>
+        <v>500597</v>
       </c>
       <c r="S2">
-        <v>499784</v>
+        <v>500991</v>
       </c>
       <c r="T2">
-        <v>500412</v>
+        <v>498869</v>
       </c>
     </row>
     <row r="3" spans="1:20">
       <c r="A3">
-        <v>0.050146</v>
+        <v>0.0499389</v>
       </c>
       <c r="B3">
-        <v>0.0499947</v>
+        <v>0.0498941</v>
       </c>
       <c r="C3">
-        <v>0.05010970000000001</v>
+        <v>0.05001999999999998</v>
       </c>
       <c r="D3">
-        <v>0.0500292</v>
+        <v>0.05007310000000001</v>
       </c>
       <c r="E3">
-        <v>0.04991879999999999</v>
+        <v>0.0500244</v>
       </c>
       <c r="F3">
-        <v>0.05000779999999999</v>
+        <v>0.05003159999999998</v>
       </c>
       <c r="G3">
-        <v>0.05004360000000002</v>
+        <v>0.05007320000000004</v>
       </c>
       <c r="H3">
-        <v>0.05002230000000002</v>
+        <v>0.04998369999999996</v>
       </c>
       <c r="I3">
-        <v>0.04998429999999998</v>
+        <v>0.04998540000000001</v>
       </c>
       <c r="J3">
-        <v>0.04988680000000001</v>
+        <v>0.04998659999999999</v>
       </c>
       <c r="K3">
-        <v>0.05011200000000005</v>
+        <v>0.05001580000000005</v>
       </c>
       <c r="L3">
-        <v>0.04974649999999992</v>
+        <v>0.04994569999999998</v>
       </c>
       <c r="M3">
-        <v>0.04999609999999999</v>
+        <v>0.05002180000000001</v>
       </c>
       <c r="N3">
-        <v>0.05004760000000008</v>
+        <v>0.04991879999999993</v>
       </c>
       <c r="O3">
-        <v>0.04998799999999992</v>
+        <v>0.05008800000000002</v>
       </c>
       <c r="P3">
-        <v>0.04997879999999999</v>
+        <v>0.05002450000000003</v>
       </c>
       <c r="Q3">
-        <v>0.04995990000000006</v>
+        <v>0.04992870000000005</v>
       </c>
       <c r="R3">
-        <v>0.05000830000000001</v>
+        <v>0.05005969999999993</v>
       </c>
       <c r="S3">
-        <v>0.04997839999999998</v>
+        <v>0.05009910000000006</v>
       </c>
       <c r="T3">
-        <v>0.05004120000000001</v>
+        <v>0.04988689999999996</v>
       </c>
     </row>
   </sheetData>

--- a/Images/1/10000000StatisticalSeries.xlsx
+++ b/Images/1/10000000StatisticalSeries.xlsx
@@ -16,84 +16,84 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
-    <t>[ 2.000000,
- 2.200000 )</t>
-  </si>
-  <si>
-    <t>[ 2.200000,
- 2.400000 )</t>
-  </si>
-  <si>
-    <t>[ 2.400000,
- 2.600000 )</t>
-  </si>
-  <si>
-    <t>[ 2.600000,
- 2.800000 )</t>
-  </si>
-  <si>
-    <t>[ 2.800000,
- 3.000000 )</t>
-  </si>
-  <si>
-    <t>[ 3.000000,
- 3.200000 )</t>
-  </si>
-  <si>
-    <t>[ 3.200000,
- 3.400000 )</t>
-  </si>
-  <si>
-    <t>[ 3.400000,
- 3.600000 )</t>
-  </si>
-  <si>
-    <t>[ 3.600000,
- 3.800000 )</t>
-  </si>
-  <si>
-    <t>[ 3.800000,
- 4.000000 )</t>
-  </si>
-  <si>
-    <t>[ 4.000000,
- 4.200000 )</t>
-  </si>
-  <si>
-    <t>[ 4.200000,
- 4.400000 )</t>
-  </si>
-  <si>
-    <t>[ 4.400000,
- 4.600000 )</t>
-  </si>
-  <si>
-    <t>[ 4.600000,
- 4.800000 )</t>
-  </si>
-  <si>
-    <t>[ 4.800000,
- 5.000000 )</t>
-  </si>
-  <si>
-    <t>[ 5.000000,
- 5.200000 )</t>
-  </si>
-  <si>
-    <t>[ 5.200000,
- 5.400000 )</t>
-  </si>
-  <si>
-    <t>[ 5.400000,
- 5.600000 )</t>
-  </si>
-  <si>
-    <t>[ 5.600000,
- 5.800000 )</t>
-  </si>
-  <si>
-    <t>[ 5.800000,
- 6.000000 ]</t>
+    <t>[ 2.0,
+ 2.2 )</t>
+  </si>
+  <si>
+    <t>[ 2.2,
+ 2.4 )</t>
+  </si>
+  <si>
+    <t>[ 2.4,
+ 2.6 )</t>
+  </si>
+  <si>
+    <t>[ 2.6,
+ 2.8 )</t>
+  </si>
+  <si>
+    <t>[ 2.8,
+ 3.0 )</t>
+  </si>
+  <si>
+    <t>[ 3.0,
+ 3.2 )</t>
+  </si>
+  <si>
+    <t>[ 3.2,
+ 3.4 )</t>
+  </si>
+  <si>
+    <t>[ 3.4,
+ 3.6 )</t>
+  </si>
+  <si>
+    <t>[ 3.6,
+ 3.8 )</t>
+  </si>
+  <si>
+    <t>[ 3.8,
+ 4.0 )</t>
+  </si>
+  <si>
+    <t>[ 4.0,
+ 4.2 )</t>
+  </si>
+  <si>
+    <t>[ 4.2,
+ 4.4 )</t>
+  </si>
+  <si>
+    <t>[ 4.4,
+ 4.6 )</t>
+  </si>
+  <si>
+    <t>[ 4.6,
+ 4.8 )</t>
+  </si>
+  <si>
+    <t>[ 4.8,
+ 5.0 )</t>
+  </si>
+  <si>
+    <t>[ 5.0,
+ 5.2 )</t>
+  </si>
+  <si>
+    <t>[ 5.2,
+ 5.4 )</t>
+  </si>
+  <si>
+    <t>[ 5.4,
+ 5.6 )</t>
+  </si>
+  <si>
+    <t>[ 5.6,
+ 5.8 )</t>
+  </si>
+  <si>
+    <t>[ 5.8,
+ 6.0 ]</t>
   </si>
 </sst>
 </file>
@@ -425,193 +425,227 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T3"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:20">
+    <row r="1" spans="1:3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1">
+        <v>500235</v>
+      </c>
+      <c r="C1">
+        <v>0.0500235</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="B2">
+        <v>499451</v>
+      </c>
+      <c r="C2">
+        <v>0.04994510000000001</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="B3">
+        <v>500030</v>
+      </c>
+      <c r="C3">
+        <v>0.05000300000000001</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="B4">
+        <v>500335</v>
+      </c>
+      <c r="C4">
+        <v>0.05003349999999998</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="B5">
+        <v>498752</v>
+      </c>
+      <c r="C5">
+        <v>0.04987520000000001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="B6">
+        <v>500500</v>
+      </c>
+      <c r="C6">
+        <v>0.05004999999999998</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="B7">
+        <v>499925</v>
+      </c>
+      <c r="C7">
+        <v>0.0499925</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="B8">
+        <v>499362</v>
+      </c>
+      <c r="C8">
+        <v>0.04993620000000004</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="B9">
+        <v>499298</v>
+      </c>
+      <c r="C9">
+        <v>0.04992979999999997</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="B10">
+        <v>499377</v>
+      </c>
+      <c r="C10">
+        <v>0.04993770000000003</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="B11">
+        <v>501971</v>
+      </c>
+      <c r="C11">
+        <v>0.05019709999999994</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="B12">
+        <v>500836</v>
+      </c>
+      <c r="C12">
+        <v>0.05008360000000001</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+      <c r="B13">
+        <v>499607</v>
+      </c>
+      <c r="C13">
+        <v>0.04996070000000008</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
         <v>13</v>
       </c>
-      <c r="O1" t="s">
+      <c r="B14">
+        <v>500305</v>
+      </c>
+      <c r="C14">
+        <v>0.05003049999999998</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" t="s">
         <v>14</v>
       </c>
-      <c r="P1" t="s">
+      <c r="B15">
+        <v>500062</v>
+      </c>
+      <c r="C15">
+        <v>0.0500062</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="B16">
+        <v>499942</v>
+      </c>
+      <c r="C16">
+        <v>0.04999419999999999</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" t="s">
         <v>16</v>
       </c>
-      <c r="R1" t="s">
+      <c r="B17">
+        <v>501956</v>
+      </c>
+      <c r="C17">
+        <v>0.05019560000000001</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" t="s">
         <v>17</v>
       </c>
-      <c r="S1" t="s">
+      <c r="B18">
+        <v>499180</v>
+      </c>
+      <c r="C18">
+        <v>0.04991800000000002</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" t="s">
         <v>18</v>
       </c>
-      <c r="T1" t="s">
+      <c r="B19">
+        <v>499245</v>
+      </c>
+      <c r="C19">
+        <v>0.04992449999999993</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="2" spans="1:20">
-      <c r="A2">
-        <v>499389</v>
-      </c>
-      <c r="B2">
-        <v>498941</v>
-      </c>
-      <c r="C2">
-        <v>500200</v>
-      </c>
-      <c r="D2">
-        <v>500731</v>
-      </c>
-      <c r="E2">
-        <v>500244</v>
-      </c>
-      <c r="F2">
-        <v>500316</v>
-      </c>
-      <c r="G2">
-        <v>500732</v>
-      </c>
-      <c r="H2">
-        <v>499837</v>
-      </c>
-      <c r="I2">
-        <v>499854</v>
-      </c>
-      <c r="J2">
-        <v>499866</v>
-      </c>
-      <c r="K2">
-        <v>500158</v>
-      </c>
-      <c r="L2">
-        <v>499457</v>
-      </c>
-      <c r="M2">
-        <v>500218</v>
-      </c>
-      <c r="N2">
-        <v>499188</v>
-      </c>
-      <c r="O2">
-        <v>500880</v>
-      </c>
-      <c r="P2">
-        <v>500245</v>
-      </c>
-      <c r="Q2">
-        <v>499287</v>
-      </c>
-      <c r="R2">
-        <v>500597</v>
-      </c>
-      <c r="S2">
-        <v>500991</v>
-      </c>
-      <c r="T2">
-        <v>498869</v>
-      </c>
-    </row>
-    <row r="3" spans="1:20">
-      <c r="A3">
-        <v>0.0499389</v>
-      </c>
-      <c r="B3">
-        <v>0.0498941</v>
-      </c>
-      <c r="C3">
-        <v>0.05001999999999998</v>
-      </c>
-      <c r="D3">
-        <v>0.05007310000000001</v>
-      </c>
-      <c r="E3">
-        <v>0.0500244</v>
-      </c>
-      <c r="F3">
-        <v>0.05003159999999998</v>
-      </c>
-      <c r="G3">
-        <v>0.05007320000000004</v>
-      </c>
-      <c r="H3">
-        <v>0.04998369999999996</v>
-      </c>
-      <c r="I3">
-        <v>0.04998540000000001</v>
-      </c>
-      <c r="J3">
-        <v>0.04998659999999999</v>
-      </c>
-      <c r="K3">
-        <v>0.05001580000000005</v>
-      </c>
-      <c r="L3">
-        <v>0.04994569999999998</v>
-      </c>
-      <c r="M3">
-        <v>0.05002180000000001</v>
-      </c>
-      <c r="N3">
-        <v>0.04991879999999993</v>
-      </c>
-      <c r="O3">
-        <v>0.05008800000000002</v>
-      </c>
-      <c r="P3">
-        <v>0.05002450000000003</v>
-      </c>
-      <c r="Q3">
-        <v>0.04992870000000005</v>
-      </c>
-      <c r="R3">
-        <v>0.05005969999999993</v>
-      </c>
-      <c r="S3">
-        <v>0.05009910000000006</v>
-      </c>
-      <c r="T3">
-        <v>0.04988689999999996</v>
+      <c r="B20">
+        <v>499631</v>
+      </c>
+      <c r="C20">
+        <v>0.04996310000000004</v>
       </c>
     </row>
   </sheetData>
